--- a/static/otchety/oneischool/oneischool_title_description.xlsx
+++ b/static/otchety/oneischool/oneischool_title_description.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Title и Description" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Title и Description" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Title и Description'!$A$1:$H$171</definedName>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -65,6 +68,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -441,6 +445,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="90" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,6 +489,11 @@
           <t>Длина Description</t>
         </is>
       </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Запросы</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -522,6 +532,7 @@
       <c r="H2" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -560,6 +571,7 @@
       <c r="H3" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -598,6 +610,7 @@
       <c r="H4" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -636,6 +649,20 @@
       <c r="H5" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>one international school
+international schools in moscow
+international schools in moscow russia
+one school
+one! international school
+школа one international school
+one international school стоимость
+international schools in russia
+best international schools in moscow
+one international school хорошевский</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -674,6 +701,11 @@
       <c r="H6" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>vosiq international school отзывы</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -712,6 +744,20 @@
       <c r="H7" s="2" t="n">
         <v>152</v>
       </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>подготовка к школе
+подготовка детей к обучению в школе
+подготовка ребенка к школе 1 класс
+дошкольная подготовка
+подготовка детей к школе
+подготовка ребенка к школе дома
+дошкольная подготовка детей к школе
+подготовка детей дошкольного возраста к школе
+подготовка ребенка к школе
+как записать ребенка на подготовку к школе</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -750,6 +796,7 @@
       <c r="H8" s="2" t="n">
         <v>146</v>
       </c>
+      <c r="I8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -788,6 +835,7 @@
       <c r="H9" s="2" t="n">
         <v>148</v>
       </c>
+      <c r="I9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -826,6 +874,20 @@
       <c r="H10" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>детский сад жк хорошевский
+частный детский сад хорошево
+детский сад в районе хорошево мневники
+частный детский сад хорошево мневники
+частный детский сад хорошево-мневники
+детский сад октябрьское поле
+детский сад хорошево мневники
+частный детский сад мневники
+частные детский сад октябрьское поле
+хорошевский детский сад</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -864,6 +926,12 @@
       <c r="H11" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>детский сад маяковская
+частный детский сад маяковская</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -902,6 +970,20 @@
       <c r="H12" s="2" t="n">
         <v>165</v>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>детский сад раменки
+частный детский сад раменки москва
+частный сад раменки
+платный садик раменки
+платный детский садик в раменках
+частный детский сад с лицензией раменки
+детский сад мосфильмовская
+детский сад на мосфильмовской
+частный сад в раменках
+детский сад в раменках москва</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -940,6 +1022,20 @@
       <c r="H13" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>частный детский сад
+частный детский сад москва
+частные детские сады москва
+международный детский сад
+английский детский сад в москве
+английский частный детский сад москва
+частный английский детский сад
+английский садик в москве
+международный детский сад москва
+москва частный детский сад</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -978,6 +1074,20 @@
       <c r="H14" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>английская школа хорошево мневники
+частная школа хорошевская
+частные школы хорошевский район
+школа в жк хорошевский
+частная школа октябрьское поле
+частные школы октябрьское поле
+частные школы в хорошево мневниках
+школа в жк хорошевский москва официальный сайт
+школы хорошевского района
+школа октябрьское поле</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1016,6 +1126,20 @@
       <c r="H15" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>частная школа раменки
+школа на мосфильмовской
+частная школа мосфильмовская
+частная школа на мосфильмовской
+школа мосфильмовская
+школа на мосфильмовской 88
+школа на мосфильмовской улице
+мосфильмовская улица школа
+школа в раменках частная
+школы на мосфильмовской улице</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1054,6 +1178,20 @@
       <c r="H16" s="2" t="n">
         <v>152</v>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>частные школы москвы
+частная школа москва
+частная школа
+билингвальная школа
+частные школы москва
+частная английская школа в москве
+английская школа в москве
+частная школа в москве
+частные школы в москве
+частные английские школы</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1092,6 +1230,7 @@
       <c r="H17" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1130,6 +1269,7 @@
       <c r="H18" s="2" t="n">
         <v>145</v>
       </c>
+      <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1168,6 +1308,7 @@
       <c r="H19" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1206,6 +1347,7 @@
       <c r="H20" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1244,6 +1386,7 @@
       <c r="H21" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1282,6 +1425,7 @@
       <c r="H22" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1320,6 +1464,7 @@
       <c r="H23" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1358,6 +1503,7 @@
       <c r="H24" s="2" t="n">
         <v>143</v>
       </c>
+      <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1396,6 +1542,11 @@
       <c r="H25" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>консультация по поступлению в зарубежные вузы</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1434,6 +1585,7 @@
       <c r="H26" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1472,6 +1624,7 @@
       <c r="H27" s="2" t="n">
         <v>164</v>
       </c>
+      <c r="I27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1510,6 +1663,7 @@
       <c r="H28" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1548,6 +1702,7 @@
       <c r="H29" s="2" t="n">
         <v>149</v>
       </c>
+      <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1586,6 +1741,7 @@
       <c r="H30" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1624,6 +1780,7 @@
       <c r="H31" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1662,6 +1819,7 @@
       <c r="H32" s="2" t="n">
         <v>148</v>
       </c>
+      <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1700,6 +1858,7 @@
       <c r="H33" s="2" t="n">
         <v>153</v>
       </c>
+      <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1738,6 +1897,7 @@
       <c r="H34" s="2" t="n">
         <v>156</v>
       </c>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1776,6 +1936,7 @@
       <c r="H35" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1814,6 +1975,7 @@
       <c r="H36" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1852,6 +2014,7 @@
       <c r="H37" s="2" t="n">
         <v>152</v>
       </c>
+      <c r="I37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1890,6 +2053,7 @@
       <c r="H38" s="2" t="n">
         <v>156</v>
       </c>
+      <c r="I38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1928,6 +2092,7 @@
       <c r="H39" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1966,6 +2131,7 @@
       <c r="H40" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2004,6 +2170,7 @@
       <c r="H41" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2042,6 +2209,7 @@
       <c r="H42" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2080,6 +2248,7 @@
       <c r="H43" s="2" t="n">
         <v>152</v>
       </c>
+      <c r="I43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2118,6 +2287,7 @@
       <c r="H44" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2156,6 +2326,7 @@
       <c r="H45" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2194,6 +2365,7 @@
       <c r="H46" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2232,6 +2404,7 @@
       <c r="H47" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2270,6 +2443,7 @@
       <c r="H48" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2308,6 +2482,7 @@
       <c r="H49" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2346,6 +2521,7 @@
       <c r="H50" s="2" t="n">
         <v>146</v>
       </c>
+      <c r="I50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2384,6 +2560,7 @@
       <c r="H51" s="2" t="n">
         <v>151</v>
       </c>
+      <c r="I51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2422,6 +2599,7 @@
       <c r="H52" s="2" t="n">
         <v>149</v>
       </c>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2460,6 +2638,7 @@
       <c r="H53" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2498,6 +2677,7 @@
       <c r="H54" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2536,6 +2716,7 @@
       <c r="H55" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2574,6 +2755,7 @@
       <c r="H56" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2612,6 +2794,7 @@
       <c r="H57" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2650,6 +2833,7 @@
       <c r="H58" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2688,6 +2872,7 @@
       <c r="H59" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2726,6 +2911,7 @@
       <c r="H60" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2764,6 +2950,7 @@
       <c r="H61" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2802,6 +2989,7 @@
       <c r="H62" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2840,6 +3028,7 @@
       <c r="H63" s="2" t="n">
         <v>145</v>
       </c>
+      <c r="I63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2878,6 +3067,7 @@
       <c r="H64" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2916,6 +3106,7 @@
       <c r="H65" s="2" t="n">
         <v>149</v>
       </c>
+      <c r="I65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2954,6 +3145,7 @@
       <c r="H66" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2992,6 +3184,7 @@
       <c r="H67" s="2" t="n">
         <v>144</v>
       </c>
+      <c r="I67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3030,6 +3223,7 @@
       <c r="H68" s="2" t="n">
         <v>143</v>
       </c>
+      <c r="I68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3068,6 +3262,7 @@
       <c r="H69" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3106,6 +3301,7 @@
       <c r="H70" s="2" t="n">
         <v>151</v>
       </c>
+      <c r="I70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3144,6 +3340,7 @@
       <c r="H71" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3182,6 +3379,7 @@
       <c r="H72" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3220,6 +3418,7 @@
       <c r="H73" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3258,6 +3457,7 @@
       <c r="H74" s="2" t="n">
         <v>153</v>
       </c>
+      <c r="I74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3296,6 +3496,7 @@
       <c r="H75" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3334,6 +3535,7 @@
       <c r="H76" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3372,6 +3574,7 @@
       <c r="H77" s="2" t="n">
         <v>165</v>
       </c>
+      <c r="I77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3410,6 +3613,7 @@
       <c r="H78" s="2" t="n">
         <v>156</v>
       </c>
+      <c r="I78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3448,6 +3652,7 @@
       <c r="H79" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3486,6 +3691,11 @@
       <c r="H80" s="2" t="n">
         <v>146</v>
       </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>кейс курсы английского языка</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3524,6 +3734,7 @@
       <c r="H81" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3562,6 +3773,7 @@
       <c r="H82" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3600,6 +3812,7 @@
       <c r="H83" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3638,6 +3851,7 @@
       <c r="H84" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3676,6 +3890,7 @@
       <c r="H85" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3714,6 +3929,7 @@
       <c r="H86" s="2" t="n">
         <v>145</v>
       </c>
+      <c r="I86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3752,6 +3968,7 @@
       <c r="H87" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3790,6 +4007,7 @@
       <c r="H88" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3828,6 +4046,7 @@
       <c r="H89" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3866,6 +4085,17 @@
       <c r="H90" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>профессии будущего
+какие специальности будут востребованы в будущем
+профессия будущего
+какие работы будут востребованы в будущем
+специальности будущего
+профессий будущего
+какие гуманитарные профессии будут востребованы в будущем</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3904,6 +4134,7 @@
       <c r="H91" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3942,6 +4173,12 @@
       <c r="H92" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>независимая диагностика
+независимое тестирование</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3980,6 +4217,7 @@
       <c r="H93" s="2" t="n">
         <v>153</v>
       </c>
+      <c r="I93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4018,6 +4256,14 @@
       <c r="H94" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>что делать если учитель занижает оценки
+учитель занижает оценки
+почему учитель занижает оценки
+учитель занижает оценки ребенку что делать</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4056,6 +4302,13 @@
       <c r="H95" s="2" t="n">
         <v>149</v>
       </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>чем занять подростка летом
+чем занять ребенка летом 12 лет
+чем заняться на каникулах летом</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4094,6 +4347,13 @@
       <c r="H96" s="2" t="n">
         <v>151</v>
       </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>как сдать огэ по математике
+как легко сдать огэ по математике
+сложно ли сдать огэ по математике</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4132,6 +4392,7 @@
       <c r="H97" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4170,6 +4431,19 @@
       <c r="H98" s="2" t="n">
         <v>153</v>
       </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>мцко диагностика
+диагностика мцко
+что такое мцко
+что такое диагностика мцко
+диагностика мцко это
+диагностики мцко
+диагностика мцко что это
+мцко диагностики
+что такое диагностика</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4208,6 +4482,7 @@
       <c r="H99" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4246,6 +4521,7 @@
       <c r="H100" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4284,6 +4560,7 @@
       <c r="H101" s="2" t="n">
         <v>152</v>
       </c>
+      <c r="I101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4322,6 +4599,7 @@
       <c r="H102" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4360,6 +4638,7 @@
       <c r="H103" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4398,6 +4677,7 @@
       <c r="H104" s="2" t="n">
         <v>165</v>
       </c>
+      <c r="I104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4436,6 +4716,7 @@
       <c r="H105" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4474,6 +4755,13 @@
       <c r="H106" s="2" t="n">
         <v>165</v>
       </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>у ребенка нет интереса к учебе
+у ребенка пропал интерес к учебе
+ребенок потерял интерес к учебе</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4512,6 +4800,7 @@
       <c r="H107" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4550,6 +4839,7 @@
       <c r="H108" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4588,6 +4878,7 @@
       <c r="H109" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4626,6 +4917,13 @@
       <c r="H110" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>проблема обучения математике
+обучение математике
+математика обучение</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4664,6 +4962,11 @@
       <c r="H111" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>современное воспитание и развитие детей</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4702,6 +5005,11 @@
       <c r="H112" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>международные олимпиады</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4740,6 +5048,13 @@
       <c r="H113" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>как воспитать билингва
+ребенок билингв
+как воспитать ребенка билингва</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4778,6 +5093,7 @@
       <c r="H114" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4816,6 +5132,7 @@
       <c r="H115" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4854,6 +5171,7 @@
       <c r="H116" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4892,6 +5210,7 @@
       <c r="H117" s="2" t="n">
         <v>164</v>
       </c>
+      <c r="I117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4930,6 +5249,16 @@
       <c r="H118" s="2" t="n">
         <v>164</v>
       </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>урок технологии
+технология урок
+урок технология
+что за урок технология
+урок по технологии
+урок технологии это</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4968,6 +5297,7 @@
       <c r="H119" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5006,6 +5336,7 @@
       <c r="H120" s="2" t="n">
         <v>156</v>
       </c>
+      <c r="I120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5044,6 +5375,7 @@
       <c r="H121" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -5082,6 +5414,7 @@
       <c r="H122" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5120,6 +5453,7 @@
       <c r="H123" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5158,6 +5492,7 @@
       <c r="H124" s="2" t="n">
         <v>151</v>
       </c>
+      <c r="I124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5196,6 +5531,16 @@
       <c r="H125" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>зачем нужна литература
+что изучает литература
+зачем изучать литературу
+зачем нужна художественная литература
+зачем нужна литература человеку
+зачем нужна литература в жизни</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5234,6 +5579,7 @@
       <c r="H126" s="2" t="n">
         <v>151</v>
       </c>
+      <c r="I126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5272,6 +5618,7 @@
       <c r="H127" s="2" t="n">
         <v>153</v>
       </c>
+      <c r="I127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5310,6 +5657,7 @@
       <c r="H128" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5348,6 +5696,7 @@
       <c r="H129" s="2" t="n">
         <v>153</v>
       </c>
+      <c r="I129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5386,6 +5735,7 @@
       <c r="H130" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5424,6 +5774,7 @@
       <c r="H131" s="2" t="n">
         <v>155</v>
       </c>
+      <c r="I131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5462,6 +5813,7 @@
       <c r="H132" s="2" t="n">
         <v>149</v>
       </c>
+      <c r="I132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5500,6 +5852,7 @@
       <c r="H133" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5538,6 +5891,7 @@
       <c r="H134" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5576,6 +5930,16 @@
       <c r="H135" s="2" t="n">
         <v>148</v>
       </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>сертификат toefl
+toefl сертификат
+сертификат toefl как получить
+как получить сертификат toefl
+для чего нужен toefl
+сертификат toefl или ielts как получить</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5614,6 +5978,7 @@
       <c r="H136" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="I136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -5652,6 +6017,14 @@
       <c r="H137" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>международная математическая олимпиада
+международная олимпиада по математике
+международные математические олимпиады
+международные олимпиады по математике</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5690,6 +6063,12 @@
       <c r="H138" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>как исправить почерк
+некрасивый почерк</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5728,6 +6107,19 @@
       <c r="H139" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>подготовка к cae
+cae подготовка к экзамену
+подготовка к cpe
+подготовка к экзамену cae
+как сдать cae
+cae экзамен
+cae экзамен по английскому
+cpe как сдать
+cae подготовка</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5766,6 +6158,18 @@
       <c r="H140" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>sat экзамен
+экзамен sat это
+подготовка к sat
+экзамен sat
+экзамен sat что это
+sat экзамен что это
+подготовка к экзамену sat
+sat это экзамен</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -5804,6 +6208,7 @@
       <c r="H141" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5842,6 +6247,7 @@
       <c r="H142" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5880,6 +6286,7 @@
       <c r="H143" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5918,6 +6325,7 @@
       <c r="H144" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5956,6 +6364,7 @@
       <c r="H145" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -5994,6 +6403,7 @@
       <c r="H146" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -6032,6 +6442,7 @@
       <c r="H147" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -6070,6 +6481,7 @@
       <c r="H148" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="I148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -6108,6 +6520,7 @@
       <c r="H149" s="2" t="n">
         <v>156</v>
       </c>
+      <c r="I149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -6146,6 +6559,7 @@
       <c r="H150" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6184,6 +6598,7 @@
       <c r="H151" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6222,6 +6637,7 @@
       <c r="H152" s="2" t="n">
         <v>165</v>
       </c>
+      <c r="I152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6260,6 +6676,7 @@
       <c r="H153" s="2" t="n">
         <v>164</v>
       </c>
+      <c r="I153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6298,6 +6715,7 @@
       <c r="H154" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -6336,6 +6754,7 @@
       <c r="H155" s="2" t="n">
         <v>148</v>
       </c>
+      <c r="I155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -6374,6 +6793,7 @@
       <c r="H156" s="2" t="n">
         <v>142</v>
       </c>
+      <c r="I156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6412,6 +6832,7 @@
       <c r="H157" s="2" t="n">
         <v>152</v>
       </c>
+      <c r="I157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6450,6 +6871,7 @@
       <c r="H158" s="2" t="n">
         <v>153</v>
       </c>
+      <c r="I158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -6488,6 +6910,7 @@
       <c r="H159" s="2" t="n">
         <v>145</v>
       </c>
+      <c r="I159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -6526,6 +6949,7 @@
       <c r="H160" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -6564,6 +6988,7 @@
       <c r="H161" s="2" t="n">
         <v>162</v>
       </c>
+      <c r="I161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -6602,6 +7027,12 @@
       <c r="H162" s="2" t="n">
         <v>157</v>
       </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>поступление в зарубежный вуз
+подготовка ребенка</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -6640,6 +7071,7 @@
       <c r="H163" s="2" t="n">
         <v>158</v>
       </c>
+      <c r="I163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -6678,6 +7110,7 @@
       <c r="H164" s="2" t="n">
         <v>142</v>
       </c>
+      <c r="I164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -6716,6 +7149,7 @@
       <c r="H165" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -6754,6 +7188,11 @@
       <c r="H166" s="2" t="n">
         <v>161</v>
       </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>переводите ребенок</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6792,6 +7231,7 @@
       <c r="H167" s="2" t="n">
         <v>163</v>
       </c>
+      <c r="I167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6830,6 +7270,7 @@
       <c r="H168" s="2" t="n">
         <v>160</v>
       </c>
+      <c r="I168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -6868,6 +7309,16 @@
       <c r="H169" s="2" t="n">
         <v>151</v>
       </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>монтессори методика
+методика монтессори
+монтессори методика раннего развития
+система монтессори
+метод монтессори
+методика раннего развития марии монтессори</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -6906,6 +7357,7 @@
       <c r="H170" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="I170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -6943,6 +7395,12 @@
       </c>
       <c r="H171" s="2" t="n">
         <v>150</v>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>билингвальное обучение это
+билингвальное обучение</t>
+        </is>
       </c>
     </row>
   </sheetData>
